--- a/public/templates/Vendor_sample_template.xlsx
+++ b/public/templates/Vendor_sample_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Vendor Name</t>
   </si>
@@ -107,25 +107,16 @@
     <t>GST Registered</t>
   </si>
   <si>
+    <t>RCM Applicable</t>
+  </si>
+  <si>
     <t>GSTIN No.</t>
   </si>
   <si>
     <t>TDS Applicable</t>
   </si>
   <si>
-    <t>TDS WEF Date</t>
-  </si>
-  <si>
     <t>TDS Certificate No.</t>
-  </si>
-  <si>
-    <t>TDS Tax %</t>
-  </si>
-  <si>
-    <t>TDS Category</t>
-  </si>
-  <si>
-    <t>TDS Value Cap</t>
   </si>
   <si>
     <t>TAN No.</t>
@@ -861,7 +852,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1192,8 +1183,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AH10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.1416666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" style="2" customWidth="1"/>
@@ -1208,19 +1199,19 @@
     <col min="18" max="18" width="12.8583333333333" style="2" customWidth="1"/>
     <col min="19" max="25" width="9.14166666666667" style="2"/>
     <col min="26" max="26" width="11.425" style="2" customWidth="1"/>
-    <col min="27" max="27" width="9.14166666666667" style="2"/>
-    <col min="28" max="28" width="11.425" style="2" customWidth="1"/>
-    <col min="29" max="29" width="9.14166666666667" style="2"/>
+    <col min="27" max="27" width="10.3" style="2" customWidth="1"/>
+    <col min="28" max="28" width="9.14166666666667" style="2"/>
+    <col min="29" max="29" width="11.425" style="2" customWidth="1"/>
     <col min="30" max="30" width="14.1416666666667" style="2" customWidth="1"/>
-    <col min="31" max="34" width="10.8583333333333" style="2" customWidth="1"/>
-    <col min="35" max="35" width="11.1416666666667" style="2" customWidth="1"/>
-    <col min="36" max="36" width="9.14166666666667" style="2"/>
-    <col min="37" max="37" width="13.2833333333333" style="2" customWidth="1"/>
-    <col min="38" max="16383" width="9.14166666666667" style="2"/>
-    <col min="16384" max="16384" width="9" style="2"/>
+    <col min="31" max="31" width="10.8583333333333" style="2" customWidth="1"/>
+    <col min="32" max="32" width="11.1416666666667" style="2" customWidth="1"/>
+    <col min="33" max="33" width="9.14166666666667" style="2"/>
+    <col min="34" max="34" width="13.2833333333333" style="2" customWidth="1"/>
+    <col min="35" max="16380" width="9.14166666666667" style="2"/>
+    <col min="16381" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:37">
+    <row r="1" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:34">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1323,32 +1314,23 @@
       <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>36</v>
-      </c>
     </row>
-    <row r="2" ht="99.75" spans="1:37">
+    <row r="2" ht="96.6" spans="1:34">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1360,7 +1342,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1370,39 +1352,28 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6" t="s">
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AC2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:34">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1437,11 +1408,8 @@
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="7"/>
-      <c r="AK3" s="7"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:34">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1476,11 +1444,8 @@
       <c r="AF4" s="7"/>
       <c r="AG4" s="7"/>
       <c r="AH4" s="7"/>
-      <c r="AI4" s="7"/>
-      <c r="AJ4" s="7"/>
-      <c r="AK4" s="7"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:34">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1515,11 +1480,8 @@
       <c r="AF5" s="7"/>
       <c r="AG5" s="7"/>
       <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
-      <c r="AJ5" s="7"/>
-      <c r="AK5" s="7"/>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:34">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1554,11 +1516,8 @@
       <c r="AF6" s="7"/>
       <c r="AG6" s="7"/>
       <c r="AH6" s="7"/>
-      <c r="AI6" s="7"/>
-      <c r="AJ6" s="7"/>
-      <c r="AK6" s="7"/>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:34">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1593,11 +1552,8 @@
       <c r="AF7" s="7"/>
       <c r="AG7" s="7"/>
       <c r="AH7" s="7"/>
-      <c r="AI7" s="7"/>
-      <c r="AJ7" s="7"/>
-      <c r="AK7" s="7"/>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:34">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1632,11 +1588,8 @@
       <c r="AF8" s="7"/>
       <c r="AG8" s="7"/>
       <c r="AH8" s="7"/>
-      <c r="AI8" s="7"/>
-      <c r="AJ8" s="7"/>
-      <c r="AK8" s="7"/>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:34">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1671,11 +1624,8 @@
       <c r="AF9" s="7"/>
       <c r="AG9" s="7"/>
       <c r="AH9" s="7"/>
-      <c r="AI9" s="7"/>
-      <c r="AJ9" s="7"/>
-      <c r="AK9" s="7"/>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:34">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1710,9 +1660,6 @@
       <c r="AF10" s="7"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
-      <c r="AI10" s="7"/>
-      <c r="AJ10" s="7"/>
-      <c r="AK10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/templates/Vendor_sample_template.xlsx
+++ b/public/templates/Vendor_sample_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Vendor Name</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>GSTIN No.</t>
-  </si>
-  <si>
-    <t>TDS Applicable</t>
   </si>
   <si>
     <t>TDS Certificate No.</t>
@@ -151,13 +148,6 @@
   <si>
     <t>Y/N
 Yes if left blank</t>
-  </si>
-  <si>
-    <t>Y/N
-No if left blank</t>
-  </si>
-  <si>
-    <t>Mandatory if TDS applicable</t>
   </si>
   <si>
     <t>Y/N
@@ -821,7 +811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -839,9 +829,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1183,8 +1170,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <dimension ref="A1:AG2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.1416666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" style="2" customWidth="1"/>
@@ -1201,17 +1188,16 @@
     <col min="26" max="26" width="11.425" style="2" customWidth="1"/>
     <col min="27" max="27" width="10.3" style="2" customWidth="1"/>
     <col min="28" max="28" width="9.14166666666667" style="2"/>
-    <col min="29" max="29" width="11.425" style="2" customWidth="1"/>
-    <col min="30" max="30" width="14.1416666666667" style="2" customWidth="1"/>
-    <col min="31" max="31" width="10.8583333333333" style="2" customWidth="1"/>
-    <col min="32" max="32" width="11.1416666666667" style="2" customWidth="1"/>
-    <col min="33" max="33" width="9.14166666666667" style="2"/>
-    <col min="34" max="34" width="13.2833333333333" style="2" customWidth="1"/>
-    <col min="35" max="16380" width="9.14166666666667" style="2"/>
-    <col min="16381" max="16384" width="9" style="2"/>
+    <col min="29" max="29" width="14.1416666666667" style="2" customWidth="1"/>
+    <col min="30" max="30" width="10.8583333333333" style="2" customWidth="1"/>
+    <col min="31" max="31" width="11.1416666666667" style="2" customWidth="1"/>
+    <col min="32" max="32" width="9.14166666666667" style="2"/>
+    <col min="33" max="33" width="13.2833333333333" style="2" customWidth="1"/>
+    <col min="34" max="16379" width="9.14166666666667" style="2"/>
+    <col min="16380" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:34">
+    <row r="1" s="1" customFormat="1" ht="33.75" customHeight="1" spans="1:33">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1311,26 +1297,23 @@
       <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="2" ht="96.6" spans="1:34">
+    <row r="2" ht="96.6" spans="1:33">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1342,7 +1325,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1352,314 +1335,19 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
-      <c r="AC2" s="6" t="s">
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AD2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7"/>
-    </row>
-    <row r="4" spans="1:34">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
-      <c r="AE4" s="7"/>
-      <c r="AF4" s="7"/>
-      <c r="AG4" s="7"/>
-      <c r="AH4" s="7"/>
-    </row>
-    <row r="5" spans="1:34">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
-    </row>
-    <row r="6" spans="1:34">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
-      <c r="AE6" s="7"/>
-      <c r="AF6" s="7"/>
-      <c r="AG6" s="7"/>
-      <c r="AH6" s="7"/>
-    </row>
-    <row r="7" spans="1:34">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="7"/>
-      <c r="AE7" s="7"/>
-      <c r="AF7" s="7"/>
-      <c r="AG7" s="7"/>
-      <c r="AH7" s="7"/>
-    </row>
-    <row r="8" spans="1:34">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
-      <c r="AE8" s="7"/>
-      <c r="AF8" s="7"/>
-      <c r="AG8" s="7"/>
-      <c r="AH8" s="7"/>
-    </row>
-    <row r="9" spans="1:34">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-      <c r="AE9" s="7"/>
-      <c r="AF9" s="7"/>
-      <c r="AG9" s="7"/>
-      <c r="AH9" s="7"/>
-    </row>
-    <row r="10" spans="1:34">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
-      <c r="AE10" s="7"/>
-      <c r="AF10" s="7"/>
-      <c r="AG10" s="7"/>
-      <c r="AH10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/templates/Vendor_sample_template.xlsx
+++ b/public/templates/Vendor_sample_template.xlsx
@@ -154,9 +154,11 @@
 No if left blank</t>
   </si>
   <si>
-    <t>mi - Micro
-sm - Small
-me - Medium</t>
+    <t>sm - Small
+me -Medium
+pr -Producer
+tr - Trader
+bo - Brand Owner</t>
   </si>
 </sst>
 </file>
